--- a/UOcc/UOcc_Producto.xlsx
+++ b/UOcc/UOcc_Producto.xlsx
@@ -2801,13 +2801,13 @@
         <v>0.02047284864164375</v>
       </c>
       <c r="L2" s="2">
-        <v>112.2262160580291</v>
+        <v>112.3873458359547</v>
       </c>
       <c r="M2" s="2">
-        <v>0.3829317224967399</v>
+        <v>0.3834815200892618</v>
       </c>
       <c r="N2" s="2">
-        <v>0.02297590334980439</v>
+        <v>0.0230088912053557</v>
       </c>
     </row>
     <row r="3" spans="1:14">
